--- a/nyc_taxi_analysis/03_combinations/candidates_rejected_by_reason.xlsx
+++ b/nyc_taxi_analysis/03_combinations/candidates_rejected_by_reason.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
